--- a/Documentation/Test_Aid_compute_direction.xlsx
+++ b/Documentation/Test_Aid_compute_direction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krgeu\source\repos\StarTrek\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223B71E4-2EC6-4F98-B9F0-A172E9D62C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66226829-9BF9-4993-93D3-8905A62AC0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2230" yWindow="810" windowWidth="19200" windowHeight="11170" xr2:uid="{1491D021-2532-4088-A1FC-29F4D08AE674}"/>
   </bookViews>
